--- a/artfynd/A 25432-2021 artfynd.xlsx
+++ b/artfynd/A 25432-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128301345</v>
       </c>
       <c r="B2" t="n">
-        <v>106870</v>
+        <v>106878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25432-2021 artfynd.xlsx
+++ b/artfynd/A 25432-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128301345</v>
       </c>
       <c r="B2" t="n">
-        <v>106878</v>
+        <v>106971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25432-2021 artfynd.xlsx
+++ b/artfynd/A 25432-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128301345</v>
       </c>
       <c r="B2" t="n">
-        <v>106971</v>
+        <v>106994</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25432-2021 artfynd.xlsx
+++ b/artfynd/A 25432-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128301345</v>
       </c>
       <c r="B2" t="n">
-        <v>106994</v>
+        <v>107006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25432-2021 artfynd.xlsx
+++ b/artfynd/A 25432-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128301345</v>
       </c>
       <c r="B2" t="n">
-        <v>107006</v>
+        <v>107015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25432-2021 artfynd.xlsx
+++ b/artfynd/A 25432-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128301345</v>
       </c>
       <c r="B2" t="n">
-        <v>107015</v>
+        <v>107020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25432-2021 artfynd.xlsx
+++ b/artfynd/A 25432-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128301345</v>
       </c>
       <c r="B2" t="n">
-        <v>107020</v>
+        <v>107048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25432-2021 artfynd.xlsx
+++ b/artfynd/A 25432-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128301345</v>
       </c>
       <c r="B2" t="n">
-        <v>107048</v>
+        <v>107061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
